--- a/data/Model_Summary.xlsx
+++ b/data/Model_Summary.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PreslavVachev\Desktop\hmmvenv\MasterThesisTrials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76892A10-AFE0-44B0-8298-EBB30704DF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32868390-6902-4311-929D-6967F61E12A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10830" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>assets_in_model</t>
   </si>
@@ -64,6 +75,33 @@
   </si>
   <si>
     <t>^SP500TR, LT09TRUU, XAU</t>
+  </si>
+  <si>
+    <t>^SP500TR, LT13TRUU, XAU</t>
+  </si>
+  <si>
+    <t>^SP500TR, LT09TRUU, DEMUSD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check actual date plz </t>
+  </si>
+  <si>
+    <t>^SP500TR, LT13TRUU, XAU, DEMUSD</t>
+  </si>
+  <si>
+    <t>^SP500TR,DEMUSD, XAU</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>USGG3M</t>
+  </si>
+  <si>
+    <t>yield_annualized</t>
+  </si>
+  <si>
+    <t>^SP500TR,DEMUSD, XAU, LT13TRUU</t>
   </si>
 </sst>
 </file>
@@ -87,12 +125,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -107,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +162,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,105 +443,219 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.08984375" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="3" max="4" width="11.26953125" customWidth="1"/>
-    <col min="5" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.36328125" customWidth="1"/>
+    <col min="2" max="3" width="27.6328125" customWidth="1"/>
+    <col min="4" max="5" width="11.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3">
         <v>34212</v>
       </c>
-      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3">
         <v>34212</v>
       </c>
-      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3">
         <v>34059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4">
+        <v>31137</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3">
+        <v>33603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3">
+        <v>33603</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3">
+        <v>33603</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3">
+        <v>33969</v>
       </c>
     </row>
   </sheetData>

--- a/data/Model_Summary.xlsx
+++ b/data/Model_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PreslavVachev\Desktop\hmmvenv\MasterThesisTrials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32868390-6902-4311-929D-6967F61E12A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDE6421-E89D-40A4-8232-0EB1CF8CBDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10830" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10845" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t>assets_in_model</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>^SP500TR,DEMUSD, XAU, LT13TRUU</t>
+  </si>
+  <si>
+    <t>^SP500TR, XAU, Oil COMP, LT09TRUU</t>
   </si>
 </sst>
 </file>
@@ -151,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -163,6 +166,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,10 +447,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1"/>
+    <col min="1" max="1" width="32.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="27.6328125" customWidth="1"/>
     <col min="4" max="5" width="11.26953125" customWidth="1"/>
     <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
@@ -658,6 +662,29 @@
         <v>33969</v>
       </c>
     </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="5">
+        <v>33663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F11" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Model_Summary.xlsx
+++ b/data/Model_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PreslavVachev\Desktop\hmmvenv\MasterThesisTrials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDE6421-E89D-40A4-8232-0EB1CF8CBDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0F1D18-9E7F-49EE-A3F4-C3C53818F3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10845" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
   <si>
     <t>assets_in_model</t>
   </si>
@@ -128,7 +128,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,6 +138,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -154,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -167,6 +173,12 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,11 +459,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="27.6328125" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" customWidth="1"/>
+    <col min="3" max="3" width="27.6328125" customWidth="1"/>
     <col min="4" max="5" width="11.26953125" customWidth="1"/>
     <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
@@ -558,52 +571,52 @@
         <v>34059</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="7">
+        <v>36160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4">
         <v>31137</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3">
-        <v>33603</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -621,9 +634,9 @@
         <v>33603</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>10</v>
@@ -642,48 +655,68 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3">
+        <v>33603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="2">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3">
         <v>33969</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="5">
         <v>33663</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="F11" s="5"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F12" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Model_Summary.xlsx
+++ b/data/Model_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PreslavVachev\Desktop\hmmvenv\MasterThesisTrials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0F1D18-9E7F-49EE-A3F4-C3C53818F3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346E9649-0E14-4EC1-B396-6CDCCCC53517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="24">
   <si>
     <t>assets_in_model</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>^SP500TR, XAU, Oil COMP, LT09TRUU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">most stable </t>
   </si>
 </sst>
 </file>
@@ -571,7 +574,7 @@
         <v>34059</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -589,6 +592,9 @@
       </c>
       <c r="F5" s="7">
         <v>36160</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
